--- a/marketing_report/outputs/Posgrados/Matcheo_Completo/Resumen_Posgrados.xlsx
+++ b/marketing_report/outputs/Posgrados/Matcheo_Completo/Resumen_Posgrados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Metrica</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Fecha generacion</t>
   </si>
   <si>
-    <t>03/03/2026 10:24</t>
+    <t>12/03/2026 21:27</t>
   </si>
   <si>
     <t>Total registros leads (con duplicados)</t>
@@ -49,6 +49,12 @@
     <t xml:space="preserve">  - Sin match (solo lead)</t>
   </si>
   <si>
+    <t>Inscriptos campana actual (2026)</t>
+  </si>
+  <si>
+    <t>Inscriptos campana anterior (match historico)</t>
+  </si>
+  <si>
     <t>Ventana de analisis</t>
   </si>
   <si>
@@ -64,25 +70,25 @@
     <t>Tasa de conversion</t>
   </si>
   <si>
-    <t>73.33%</t>
+    <t>68.29%</t>
   </si>
   <si>
     <t>Hoja Con_Duplicados</t>
   </si>
   <si>
-    <t>157 filas - 1 por registro de lead</t>
+    <t>178 filas - 1 por registro de lead</t>
   </si>
   <si>
     <t>Hoja Deduplicados</t>
   </si>
   <si>
-    <t>127 filas - 1 por persona (mejor match)</t>
+    <t>145 filas - 1 por persona (mejor match)</t>
   </si>
   <si>
     <t>Hoja Solo_Matcheados</t>
   </si>
   <si>
-    <t>93 filas - solo personas con inscripto</t>
+    <t>100 filas - solo personas con inscripto</t>
   </si>
   <si>
     <t>Columnas totales por hoja</t>
@@ -485,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="48.7109375" customWidth="1"/>
@@ -532,7 +538,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="5">
-        <v>157</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -540,7 +546,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="5">
-        <v>127</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -548,7 +554,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="5">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -556,7 +562,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="5">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -573,7 +579,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="4">
-        <f>== MUESTRA CONVERSION (cohorte) ===</f>
+        <f>== ATRIBUCION POR CAMPANA ===</f>
         <v>0</v>
       </c>
       <c r="B12" s="4"/>
@@ -582,90 +588,117 @@
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>12</v>
+      <c r="B13" s="5">
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="5">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="4">
+        <f>== MUESTRA CONVERSION (cohorte) ===</f>
+        <v>0</v>
+      </c>
+      <c r="B16" s="4"/>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="5">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="5">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="2" t="s">
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B18" s="5">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="4">
+      <c r="B19" s="5">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="4">
         <f>== ESTRUCTURA ARCHIVO ===</f>
         <v>0</v>
       </c>
-      <c r="B18" s="4"/>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="5">
-        <v>83</v>
-      </c>
+      <c r="B22" s="4"/>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="5">
-        <v>54</v>
+        <v>19</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B26" s="5">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="5">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="5">
         <v>29</v>
       </c>
     </row>

--- a/marketing_report/outputs/Posgrados/Matcheo_Completo/Resumen_Posgrados.xlsx
+++ b/marketing_report/outputs/Posgrados/Matcheo_Completo/Resumen_Posgrados.xlsx
@@ -31,7 +31,7 @@
     <t>Fecha generacion</t>
   </si>
   <si>
-    <t>12/03/2026 21:27</t>
+    <t>14/03/2026 20:36</t>
   </si>
   <si>
     <t>Total registros leads (con duplicados)</t>
@@ -70,25 +70,25 @@
     <t>Tasa de conversion</t>
   </si>
   <si>
-    <t>68.29%</t>
+    <t>59.62%</t>
   </si>
   <si>
     <t>Hoja Con_Duplicados</t>
   </si>
   <si>
-    <t>178 filas - 1 por registro de lead</t>
+    <t>139 filas - 1 por registro de lead</t>
   </si>
   <si>
     <t>Hoja Deduplicados</t>
   </si>
   <si>
-    <t>145 filas - 1 por persona (mejor match)</t>
+    <t>111 filas - 1 por persona (mejor match)</t>
   </si>
   <si>
     <t>Hoja Solo_Matcheados</t>
   </si>
   <si>
-    <t>100 filas - solo personas con inscripto</t>
+    <t>63 filas - solo personas con inscripto</t>
   </si>
   <si>
     <t>Columnas totales por hoja</t>
@@ -538,7 +538,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="5">
-        <v>178</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -546,7 +546,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="5">
-        <v>145</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -554,7 +554,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="5">
-        <v>100</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -562,7 +562,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="5">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -589,7 +589,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="5">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -597,7 +597,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="5">
-        <v>72</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -624,7 +624,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="5">
-        <v>123</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -632,7 +632,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="5">
-        <v>84</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:2">
